--- a/VitalSigns/NordicTXTestBuild/StructureDefinition-no-domain-VitalSigns-Observation-pulse.xlsx
+++ b/VitalSigns/NordicTXTestBuild/StructureDefinition-no-domain-VitalSigns-Observation-pulse.xlsx
@@ -389,7 +389,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -618,7 +618,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -647,7 +647,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -727,7 +727,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1017,7 +1017,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1175,7 +1175,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1198,7 +1198,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1297,7 +1297,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1568,7 +1568,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1600,7 +1600,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1719,7 +1719,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1747,7 +1747,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1827,7 +1827,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1877,7 +1877,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1913,7 +1913,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1950,7 +1950,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1972,7 +1972,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -4744,7 +4744,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>207</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>230</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>245</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>259</v>
       </c>
@@ -5948,7 +5948,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>277</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>313</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>362</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>389</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>438</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>446</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>467</v>
       </c>
@@ -10780,7 +10780,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>475</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>484</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>492</v>
       </c>
@@ -14266,7 +14266,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>631</v>
       </c>
@@ -14748,7 +14748,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>641</v>
       </c>
@@ -14870,7 +14870,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>647</v>
       </c>
@@ -14992,7 +14992,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
         <v>656</v>
       </c>
@@ -15360,12 +15360,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP107">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
